--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KHAS\auto-webapp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CMTHANG\playwright-everything-main\playwright-everything-main\playwright-python\session_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AC0C70-9313-498A-98B2-5D5A3970AB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38E41BE-8BEA-4521-B3E9-CC2DFACB4324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="429" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="429" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="616">
   <si>
     <t>email</t>
   </si>
@@ -1436,373 +1436,355 @@
     <t>Ngày ra báo phí</t>
   </si>
   <si>
-    <t>882</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Không có dữ liệu</t>
+  </si>
+  <si>
+    <t>603</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>22/10/2025</t>
+  </si>
+  <si>
+    <t>01/10/2025</t>
+  </si>
+  <si>
+    <t>621</t>
+  </si>
+  <si>
+    <t>608</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
+    <t>01/11/2025</t>
+  </si>
+  <si>
+    <t>547</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>03/11/2025</t>
+  </si>
+  <si>
+    <t>287</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>14/10/2025</t>
+  </si>
+  <si>
+    <t>1,139</t>
+  </si>
+  <si>
+    <t>468</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>10/11/2025</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>431</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>473</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>17/10/2025</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>09/10/2025</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>05/11/2025</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t>677</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>488</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>31/07/2025</t>
-  </si>
-  <si>
-    <t>603</t>
-  </si>
-  <si>
-    <t>497</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>18/11/2025</t>
-  </si>
-  <si>
-    <t>01/10/2025</t>
-  </si>
-  <si>
-    <t>621</t>
-  </si>
-  <si>
-    <t>612</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>05/12/2025</t>
-  </si>
-  <si>
-    <t>01/11/2025</t>
-  </si>
-  <si>
-    <t>547</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>02/12/2025</t>
-  </si>
-  <si>
-    <t>287</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>03/12/2025</t>
-  </si>
-  <si>
-    <t>1,139</t>
-  </si>
-  <si>
-    <t>472</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>09/12/2025</t>
-  </si>
-  <si>
-    <t>504</t>
-  </si>
-  <si>
-    <t>94</t>
+    <t>16</t>
+  </si>
+  <si>
+    <t>22/09/2025</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>23/10/2025</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>553</t>
+  </si>
+  <si>
+    <t>145</t>
   </si>
   <si>
     <t>47</t>
   </si>
   <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>10/12/2025</t>
-  </si>
-  <si>
-    <t>431</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>338</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>473</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>17/10/2025</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>09/10/2025</t>
-  </si>
-  <si>
-    <t>426</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>28/08/2025</t>
-  </si>
-  <si>
-    <t>677</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>27/11/2025</t>
-  </si>
-  <si>
-    <t>488</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>10/10/2025</t>
+  </si>
+  <si>
+    <t>163</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>12/11/2025</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>06/12/2025</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>08/12/2025</t>
-  </si>
-  <si>
-    <t>553</t>
-  </si>
-  <si>
-    <t>145</t>
+    <t>200</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>CHUNG CƯ PHÚ GIA</t>
+  </si>
+  <si>
+    <t>573</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>19/07/2025</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>30/08/2025</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>30/10/2025</t>
+  </si>
+  <si>
+    <t>359</t>
   </si>
   <si>
     <t>50</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>10/10/2025</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>29/11/2025</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>CHUNG CƯ PHÚ GIA</t>
-  </si>
-  <si>
-    <t>573</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>28/11/2025</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>30/08/2025</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>298</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>511</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>19/11/2025</t>
   </si>
   <si>
     <t>Mã căn hộ</t>
@@ -2015,7 +1997,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2036,6 +2018,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2082,19 +2065,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2159,9 +2129,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2199,7 +2169,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2305,7 +2275,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2447,7 +2417,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2456,13 +2426,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="36.88671875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2470,11 +2440,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2491,338 +2461,338 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.85546875" style="11" customWidth="1"/>
+    <col min="1" max="3" width="8.88671875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="12">
+        <v>1668000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="12">
+        <v>372008</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="12">
+        <v>1091322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="12">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="12">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="B7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="12">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="11">
-        <v>1668000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="B8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="12">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>594</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="11">
-        <v>372008</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="B9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="12">
+        <v>1164464</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>595</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="11">
-        <v>1091322</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="B10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="12">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>596</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="11">
+      <c r="B11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="12">
+        <v>725184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="12">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="12">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1711582</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="12">
+        <v>805484</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="12">
+        <v>59420</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1313257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="12">
+        <v>845290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="12">
+        <v>5696588</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="12">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="12">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="12">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="12">
+        <v>790606</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="12">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="12">
+        <v>1287984</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="12">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="12">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>614</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="12">
         <v>20000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>597</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="11">
-        <v>280000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>598</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="11">
-        <v>230000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>599</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="11">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>600</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="11">
-        <v>1164464</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>601</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="11">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>602</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="11">
-        <v>725184</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>603</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="11">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>604</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="11">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>605</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="11">
-        <v>1711582</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>606</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="11">
-        <v>805484</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>607</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="11">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>608</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="11">
-        <v>59420</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="11">
-        <v>1313257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>610</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="11">
-        <v>845290</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>611</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="11">
-        <v>5696588</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>612</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="11">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="11">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>614</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="11">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="11">
-        <v>790606</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>616</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="11">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="11">
-        <v>1287984</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>618</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="11">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="11">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>620</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="11">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>621</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="11">
+      <c r="B30" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="12">
         <v>901</v>
       </c>
     </row>
@@ -2834,1185 +2804,1185 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" style="12" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="B2" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="B3" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="B4" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="B5" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="B6" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="B7" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="B8" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="B9" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="B10" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="B11" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="B12" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="B13" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="B14" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="B15" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="B16" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="B17" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="B18" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="B19" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="B20" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="B21" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="B22" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="B23" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="B24" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="B25" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="B26" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="B27" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="B28" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="B29" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="B30" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="B31" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="B32" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="B33" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="B34" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="B35" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="B36" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
+      <c r="B37" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+      <c r="B38" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="B39" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
+      <c r="B40" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="B41" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+      <c r="B42" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+      <c r="B43" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
+      <c r="B44" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+      <c r="B45" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
+      <c r="B46" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B47" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+      <c r="B47" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
+      <c r="B48" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+      <c r="B49" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="B50" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
+      <c r="B51" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+      <c r="B52" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+      <c r="B53" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+      <c r="B54" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
+      <c r="B55" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
+      <c r="B56" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="B57" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
+      <c r="B58" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
+      <c r="B59" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B60" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
+      <c r="B60" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B61" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="B61" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B62" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
+      <c r="B62" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
+      <c r="B63" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B64" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
+      <c r="B64" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B65" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="B65" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
+      <c r="B66" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B67" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="B67" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="11" t="s">
+      <c r="B68" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B69" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
+      <c r="B69" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B70" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="11" t="s">
+      <c r="B70" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B71" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
+      <c r="B71" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B72" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="11" t="s">
+      <c r="B72" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="11" t="s">
+      <c r="B73" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="11" t="s">
+      <c r="B74" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B75" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
+      <c r="B75" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B76" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
+      <c r="B76" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B77" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
+      <c r="B77" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="11" t="s">
+      <c r="B78" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B79" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
+      <c r="B79" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
+      <c r="B80" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B81" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="11" t="s">
+      <c r="B81" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B82" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="11" t="s">
+      <c r="B82" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B83" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="11" t="s">
+      <c r="B83" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B84" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="11" t="s">
+      <c r="B84" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B85" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="11" t="s">
+      <c r="B85" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B86" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="11" t="s">
+      <c r="B86" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B87" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="11" t="s">
+      <c r="B87" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B88" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="11" t="s">
+      <c r="B88" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B89" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="11" t="s">
+      <c r="B89" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B90" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="11" t="s">
+      <c r="B90" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B91" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="11" t="s">
+      <c r="B91" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B92" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="11" t="s">
+      <c r="B92" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="11" t="s">
+      <c r="B93" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B94" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="11" t="s">
+      <c r="B94" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B95" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="11" t="s">
+      <c r="B95" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B96" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="11" t="s">
+      <c r="B96" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B97" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="11" t="s">
+      <c r="B97" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B98" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="11" t="s">
+      <c r="B98" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B99" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="11" t="s">
+      <c r="B99" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B100" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="11" t="s">
+      <c r="B100" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B101" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="11" t="s">
+      <c r="B101" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B102" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="11" t="s">
+      <c r="B102" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="11" t="s">
+      <c r="B103" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B104" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="11" t="s">
+      <c r="B104" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B105" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="11" t="s">
+      <c r="B105" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B106" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="11" t="s">
+      <c r="B106" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B107" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="11" t="s">
+      <c r="B107" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B108" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="11" t="s">
+      <c r="B108" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B109" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="11" t="s">
+      <c r="B109" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B110" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="11" t="s">
+      <c r="B110" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B111" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="11" t="s">
+      <c r="B111" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B112" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="11" t="s">
+      <c r="B112" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B113" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="11" t="s">
+      <c r="B113" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B114" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="11" t="s">
+      <c r="B114" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B115" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="11" t="s">
+      <c r="B115" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B116" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="11" t="s">
+      <c r="B116" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B117" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="11" t="s">
+      <c r="B117" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B118" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="11" t="s">
+      <c r="B118" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B119" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="11" t="s">
+      <c r="B119" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B120" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="11" t="s">
+      <c r="B120" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B121" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="11" t="s">
+      <c r="B121" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B122" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="11" t="s">
+      <c r="B122" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B123" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="11" t="s">
+      <c r="B123" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B124" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="11" t="s">
+      <c r="B124" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B125" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" s="11" t="s">
+      <c r="B125" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B126" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" s="11" t="s">
+      <c r="B126" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="B127" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" s="11" t="s">
+      <c r="B127" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="B128" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" s="11" t="s">
+      <c r="B128" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B129" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" s="11" t="s">
+      <c r="B129" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B130" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" s="11" t="s">
+      <c r="B130" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B131" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" s="11" t="s">
+      <c r="B131" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B132" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" s="11" t="s">
+      <c r="B132" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B133" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" s="11" t="s">
+      <c r="B133" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B134" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" s="11" t="s">
+      <c r="B134" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B135" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" s="11" t="s">
+      <c r="B135" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B136" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" s="11" t="s">
+      <c r="B136" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B137" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" s="11" t="s">
+      <c r="B137" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B138" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" s="11" t="s">
+      <c r="B138" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B139" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" s="11" t="s">
+      <c r="B139" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B140" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" s="11" t="s">
+      <c r="B140" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="B141" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" s="11" t="s">
+      <c r="B141" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B142" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" s="11" t="s">
+      <c r="B142" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B143" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" s="11" t="s">
+      <c r="B143" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B144" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" s="11" t="s">
+      <c r="B144" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B145" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" s="11" t="s">
+      <c r="B145" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B146" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" s="11" t="s">
+      <c r="B146" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4031,30 +4001,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D236"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.109375" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="22">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="23">
         <v>45658</v>
       </c>
       <c r="B2" s="7">
@@ -4063,12 +4033,12 @@
       <c r="C2" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="25" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="22">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="23">
         <v>45659</v>
       </c>
       <c r="B3" s="7">
@@ -4077,12 +4047,12 @@
       <c r="C3" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="25" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="23">
         <v>45660</v>
       </c>
       <c r="B4" s="7">
@@ -4091,12 +4061,12 @@
       <c r="C4" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="25" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="23">
         <v>45661</v>
       </c>
       <c r="B5" s="7">
@@ -4105,12 +4075,12 @@
       <c r="C5" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="25" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="23">
         <v>45662</v>
       </c>
       <c r="B6" s="7">
@@ -4119,12 +4089,12 @@
       <c r="C6" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="25" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="23">
         <v>45663</v>
       </c>
       <c r="B7" s="7">
@@ -4133,12 +4103,12 @@
       <c r="C7" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="25" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="23">
         <v>45664</v>
       </c>
       <c r="B8" s="7">
@@ -4147,12 +4117,12 @@
       <c r="C8" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="25" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="23">
         <v>45665</v>
       </c>
       <c r="B9" s="7">
@@ -4161,12 +4131,12 @@
       <c r="C9" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="25" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="23">
         <v>45666</v>
       </c>
       <c r="B10" s="7">
@@ -4175,12 +4145,12 @@
       <c r="C10" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="25" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="23">
         <v>45667</v>
       </c>
       <c r="B11" s="7">
@@ -4189,12 +4159,12 @@
       <c r="C11" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="25" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="23">
         <v>45668</v>
       </c>
       <c r="B12" s="7">
@@ -4203,12 +4173,12 @@
       <c r="C12" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="25" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="23">
         <v>45669</v>
       </c>
       <c r="B13" s="7">
@@ -4217,12 +4187,12 @@
       <c r="C13" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="25" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="23">
         <v>45670</v>
       </c>
       <c r="B14" s="7">
@@ -4231,12 +4201,12 @@
       <c r="C14" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="25" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="23">
         <v>45671</v>
       </c>
       <c r="B15" s="7">
@@ -4245,12 +4215,12 @@
       <c r="C15" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="23">
         <v>45672</v>
       </c>
       <c r="B16" s="7">
@@ -4259,12 +4229,12 @@
       <c r="C16" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="25" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="23">
         <v>45673</v>
       </c>
       <c r="B17" s="7">
@@ -4273,12 +4243,12 @@
       <c r="C17" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="25" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="22">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="23">
         <v>45674</v>
       </c>
       <c r="B18" s="7">
@@ -4287,12 +4257,12 @@
       <c r="C18" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="25" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="22">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="23">
         <v>45675</v>
       </c>
       <c r="B19" s="7">
@@ -4301,12 +4271,12 @@
       <c r="C19" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="25" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="22">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="23">
         <v>45676</v>
       </c>
       <c r="B20" s="7">
@@ -4315,12 +4285,12 @@
       <c r="C20" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="25" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="22">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="23">
         <v>45677</v>
       </c>
       <c r="B21" s="7">
@@ -4329,12 +4299,12 @@
       <c r="C21" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="25" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="22">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="23">
         <v>45678</v>
       </c>
       <c r="B22" s="7">
@@ -4343,12 +4313,12 @@
       <c r="C22" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="25" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="22">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="23">
         <v>45679</v>
       </c>
       <c r="B23" s="7">
@@ -4357,12 +4327,12 @@
       <c r="C23" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="25" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="22">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="23">
         <v>45680</v>
       </c>
       <c r="B24" s="7">
@@ -4371,12 +4341,12 @@
       <c r="C24" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="25" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="22">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="23">
         <v>45681</v>
       </c>
       <c r="B25" s="7">
@@ -4385,12 +4355,12 @@
       <c r="C25" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="25" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="22">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="23">
         <v>45682</v>
       </c>
       <c r="B26" s="7">
@@ -4399,12 +4369,12 @@
       <c r="C26" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="25" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="22">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="23">
         <v>45683</v>
       </c>
       <c r="B27" s="7">
@@ -4413,12 +4383,12 @@
       <c r="C27" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="25" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="22">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="23">
         <v>45684</v>
       </c>
       <c r="B28" s="7">
@@ -4427,12 +4397,12 @@
       <c r="C28" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="25" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="22">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="23">
         <v>45685</v>
       </c>
       <c r="B29" s="7">
@@ -4441,12 +4411,12 @@
       <c r="C29" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="25" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="22">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="23">
         <v>45686</v>
       </c>
       <c r="B30" s="7">
@@ -4455,12 +4425,12 @@
       <c r="C30" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="25" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="22">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="23">
         <v>45687</v>
       </c>
       <c r="B31" s="7">
@@ -4469,12 +4439,12 @@
       <c r="C31" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="25" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="22">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="23">
         <v>45688</v>
       </c>
       <c r="B32" s="7">
@@ -4483,12 +4453,12 @@
       <c r="C32" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="25" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="22">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="23">
         <v>45690</v>
       </c>
       <c r="B33" s="7">
@@ -4497,12 +4467,12 @@
       <c r="C33" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="25" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="22">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="23">
         <v>45691</v>
       </c>
       <c r="B34" s="7">
@@ -4511,12 +4481,12 @@
       <c r="C34" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="25" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="22">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="23">
         <v>45692</v>
       </c>
       <c r="B35" s="7">
@@ -4525,12 +4495,12 @@
       <c r="C35" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="25" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="22">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="23">
         <v>45693</v>
       </c>
       <c r="B36" s="7">
@@ -4539,12 +4509,12 @@
       <c r="C36" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="24" t="s">
+      <c r="D36" s="25" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="22">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="23">
         <v>45694</v>
       </c>
       <c r="B37" s="7">
@@ -4553,12 +4523,12 @@
       <c r="C37" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="25" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="22">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="23">
         <v>45695</v>
       </c>
       <c r="B38" s="7">
@@ -4567,12 +4537,12 @@
       <c r="C38" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D38" s="25" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="22">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="23">
         <v>45696</v>
       </c>
       <c r="B39" s="7">
@@ -4581,12 +4551,12 @@
       <c r="C39" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D39" s="24" t="s">
+      <c r="D39" s="25" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="22">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="23">
         <v>45697</v>
       </c>
       <c r="B40" s="7">
@@ -4595,12 +4565,12 @@
       <c r="C40" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="25" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="22">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="23">
         <v>45698</v>
       </c>
       <c r="B41" s="7">
@@ -4609,12 +4579,12 @@
       <c r="C41" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D41" s="25" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="22">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="23">
         <v>45699</v>
       </c>
       <c r="B42" s="7">
@@ -4623,12 +4593,12 @@
       <c r="C42" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="25" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="22">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="23">
         <v>45700</v>
       </c>
       <c r="B43" s="7">
@@ -4637,12 +4607,12 @@
       <c r="C43" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="25" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="22">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="23">
         <v>45701</v>
       </c>
       <c r="B44" s="7">
@@ -4651,12 +4621,12 @@
       <c r="C44" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D44" s="24" t="s">
+      <c r="D44" s="25" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="22">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="23">
         <v>45702</v>
       </c>
       <c r="B45" s="7">
@@ -4665,12 +4635,12 @@
       <c r="C45" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D45" s="24" t="s">
+      <c r="D45" s="25" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="22">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="23">
         <v>45703</v>
       </c>
       <c r="B46" s="7">
@@ -4679,12 +4649,12 @@
       <c r="C46" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D46" s="24" t="s">
+      <c r="D46" s="25" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="22">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="23">
         <v>45704</v>
       </c>
       <c r="B47" s="7">
@@ -4693,12 +4663,12 @@
       <c r="C47" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D47" s="24" t="s">
+      <c r="D47" s="25" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="22">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="23">
         <v>45705</v>
       </c>
       <c r="B48" s="7">
@@ -4707,12 +4677,12 @@
       <c r="C48" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D48" s="24" t="s">
+      <c r="D48" s="25" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="22">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="23">
         <v>45706</v>
       </c>
       <c r="B49" s="7">
@@ -4721,12 +4691,12 @@
       <c r="C49" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D49" s="24" t="s">
+      <c r="D49" s="25" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="22">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="23">
         <v>45707</v>
       </c>
       <c r="B50" s="7">
@@ -4735,12 +4705,12 @@
       <c r="C50" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D50" s="24" t="s">
+      <c r="D50" s="25" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="22">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="23">
         <v>45708</v>
       </c>
       <c r="B51" s="7">
@@ -4749,12 +4719,12 @@
       <c r="C51" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D51" s="24" t="s">
+      <c r="D51" s="25" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="22">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="23">
         <v>45709</v>
       </c>
       <c r="B52" s="7">
@@ -4763,12 +4733,12 @@
       <c r="C52" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D52" s="24" t="s">
+      <c r="D52" s="25" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="22">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="23">
         <v>45710</v>
       </c>
       <c r="B53" s="7">
@@ -4777,12 +4747,12 @@
       <c r="C53" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D53" s="24" t="s">
+      <c r="D53" s="25" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="22">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="23">
         <v>45711</v>
       </c>
       <c r="B54" s="7">
@@ -4791,12 +4761,12 @@
       <c r="C54" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D54" s="24" t="s">
+      <c r="D54" s="25" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="22">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="23">
         <v>45712</v>
       </c>
       <c r="B55" s="7">
@@ -4805,12 +4775,12 @@
       <c r="C55" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="25" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="22">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="23">
         <v>45713</v>
       </c>
       <c r="B56" s="7">
@@ -4819,12 +4789,12 @@
       <c r="C56" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D56" s="24" t="s">
+      <c r="D56" s="25" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="22">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="23">
         <v>45714</v>
       </c>
       <c r="B57" s="7">
@@ -4833,12 +4803,12 @@
       <c r="C57" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D57" s="24" t="s">
+      <c r="D57" s="25" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="22">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="23">
         <v>45715</v>
       </c>
       <c r="B58" s="7">
@@ -4847,12 +4817,12 @@
       <c r="C58" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D58" s="24" t="s">
+      <c r="D58" s="25" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="22">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="23">
         <v>45716</v>
       </c>
       <c r="B59" s="7">
@@ -4861,12 +4831,12 @@
       <c r="C59" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D59" s="24" t="s">
+      <c r="D59" s="25" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="22">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="23">
         <v>45717</v>
       </c>
       <c r="B60" s="7">
@@ -4875,12 +4845,12 @@
       <c r="C60" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="24" t="s">
+      <c r="D60" s="25" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="22">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="23">
         <v>45718</v>
       </c>
       <c r="B61" s="7">
@@ -4889,12 +4859,12 @@
       <c r="C61" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D61" s="24" t="s">
+      <c r="D61" s="25" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="22">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="23">
         <v>45719</v>
       </c>
       <c r="B62" s="7">
@@ -4903,12 +4873,12 @@
       <c r="C62" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D62" s="24" t="s">
+      <c r="D62" s="25" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="22">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="23">
         <v>45720</v>
       </c>
       <c r="B63" s="7">
@@ -4917,12 +4887,12 @@
       <c r="C63" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D63" s="24" t="s">
+      <c r="D63" s="25" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="22">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="23">
         <v>45721</v>
       </c>
       <c r="B64" s="7">
@@ -4931,12 +4901,12 @@
       <c r="C64" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D64" s="24" t="s">
+      <c r="D64" s="25" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="22">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="23">
         <v>45722</v>
       </c>
       <c r="B65" s="7">
@@ -4945,12 +4915,12 @@
       <c r="C65" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D65" s="24" t="s">
+      <c r="D65" s="25" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="22">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="23">
         <v>45723</v>
       </c>
       <c r="B66" s="7">
@@ -4959,12 +4929,12 @@
       <c r="C66" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D66" s="24" t="s">
+      <c r="D66" s="25" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="22">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="23">
         <v>45724</v>
       </c>
       <c r="B67" s="7">
@@ -4973,12 +4943,12 @@
       <c r="C67" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D67" s="24" t="s">
+      <c r="D67" s="25" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="22">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="23">
         <v>45725</v>
       </c>
       <c r="B68" s="7">
@@ -4987,12 +4957,12 @@
       <c r="C68" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D68" s="24" t="s">
+      <c r="D68" s="25" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="22">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="23">
         <v>45726</v>
       </c>
       <c r="B69" s="7">
@@ -5001,12 +4971,12 @@
       <c r="C69" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D69" s="24" t="s">
+      <c r="D69" s="25" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="22">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="23">
         <v>45727</v>
       </c>
       <c r="B70" s="7">
@@ -5015,12 +4985,12 @@
       <c r="C70" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D70" s="24" t="s">
+      <c r="D70" s="25" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="22">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="23">
         <v>45728</v>
       </c>
       <c r="B71" s="7">
@@ -5029,12 +4999,12 @@
       <c r="C71" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D71" s="24" t="s">
+      <c r="D71" s="25" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="22">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="23">
         <v>45729</v>
       </c>
       <c r="B72" s="7">
@@ -5043,12 +5013,12 @@
       <c r="C72" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D72" s="24" t="s">
+      <c r="D72" s="25" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="22">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="23">
         <v>45730</v>
       </c>
       <c r="B73" s="7">
@@ -5057,12 +5027,12 @@
       <c r="C73" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D73" s="24" t="s">
+      <c r="D73" s="25" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="22">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="23">
         <v>45731</v>
       </c>
       <c r="B74" s="7">
@@ -5071,12 +5041,12 @@
       <c r="C74" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D74" s="24" t="s">
+      <c r="D74" s="25" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="22">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="23">
         <v>45732</v>
       </c>
       <c r="B75" s="7">
@@ -5085,12 +5055,12 @@
       <c r="C75" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D75" s="24" t="s">
+      <c r="D75" s="25" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="22">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="23">
         <v>45733</v>
       </c>
       <c r="B76" s="7">
@@ -5099,12 +5069,12 @@
       <c r="C76" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D76" s="24" t="s">
+      <c r="D76" s="25" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="22">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="23">
         <v>45734</v>
       </c>
       <c r="B77" s="7">
@@ -5113,12 +5083,12 @@
       <c r="C77" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D77" s="24" t="s">
+      <c r="D77" s="25" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="22">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="23">
         <v>45735</v>
       </c>
       <c r="B78" s="7">
@@ -5127,12 +5097,12 @@
       <c r="C78" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="24" t="s">
+      <c r="D78" s="25" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="22">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="23">
         <v>45736</v>
       </c>
       <c r="B79" s="7">
@@ -5141,12 +5111,12 @@
       <c r="C79" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D79" s="24" t="s">
+      <c r="D79" s="25" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="22">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="23">
         <v>45737</v>
       </c>
       <c r="B80" s="7">
@@ -5155,12 +5125,12 @@
       <c r="C80" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D80" s="24" t="s">
+      <c r="D80" s="25" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="22">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="23">
         <v>45738</v>
       </c>
       <c r="B81" s="7">
@@ -5169,12 +5139,12 @@
       <c r="C81" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D81" s="24" t="s">
+      <c r="D81" s="25" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="22">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="23">
         <v>45739</v>
       </c>
       <c r="B82" s="7">
@@ -5183,12 +5153,12 @@
       <c r="C82" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D82" s="24" t="s">
+      <c r="D82" s="25" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="22">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="23">
         <v>45740</v>
       </c>
       <c r="B83" s="7">
@@ -5197,12 +5167,12 @@
       <c r="C83" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D83" s="24" t="s">
+      <c r="D83" s="25" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="22">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="23">
         <v>45741</v>
       </c>
       <c r="B84" s="7">
@@ -5211,12 +5181,12 @@
       <c r="C84" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D84" s="24" t="s">
+      <c r="D84" s="25" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="22">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="23">
         <v>45742</v>
       </c>
       <c r="B85" s="7">
@@ -5225,12 +5195,12 @@
       <c r="C85" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D85" s="24" t="s">
+      <c r="D85" s="25" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="22">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="23">
         <v>45743</v>
       </c>
       <c r="B86" s="7">
@@ -5239,12 +5209,12 @@
       <c r="C86" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D86" s="24" t="s">
+      <c r="D86" s="25" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="22">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="23">
         <v>45744</v>
       </c>
       <c r="B87" s="7">
@@ -5253,12 +5223,12 @@
       <c r="C87" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D87" s="24" t="s">
+      <c r="D87" s="25" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="22">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="23">
         <v>45745</v>
       </c>
       <c r="B88" s="7">
@@ -5267,12 +5237,12 @@
       <c r="C88" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D88" s="24" t="s">
+      <c r="D88" s="25" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="22">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="23">
         <v>45746</v>
       </c>
       <c r="B89" s="7">
@@ -5281,12 +5251,12 @@
       <c r="C89" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D89" s="24" t="s">
+      <c r="D89" s="25" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="22">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="23">
         <v>45747</v>
       </c>
       <c r="B90" s="7">
@@ -5295,12 +5265,12 @@
       <c r="C90" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D90" s="24" t="s">
+      <c r="D90" s="25" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="22">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="23">
         <v>45748</v>
       </c>
       <c r="B91" s="7">
@@ -5309,12 +5279,12 @@
       <c r="C91" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D91" s="24" t="s">
+      <c r="D91" s="25" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="22">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="23">
         <v>45749</v>
       </c>
       <c r="B92" s="7">
@@ -5323,12 +5293,12 @@
       <c r="C92" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D92" s="24" t="s">
+      <c r="D92" s="25" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="22">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="23">
         <v>45750</v>
       </c>
       <c r="B93" s="7">
@@ -5337,12 +5307,12 @@
       <c r="C93" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D93" s="24" t="s">
+      <c r="D93" s="25" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="22">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="23">
         <v>45751</v>
       </c>
       <c r="B94" s="7">
@@ -5351,12 +5321,12 @@
       <c r="C94" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D94" s="24" t="s">
+      <c r="D94" s="25" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="22">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="23">
         <v>45754</v>
       </c>
       <c r="B95" s="7">
@@ -5365,12 +5335,12 @@
       <c r="C95" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D95" s="24" t="s">
+      <c r="D95" s="25" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="22">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="23">
         <v>45755</v>
       </c>
       <c r="B96" s="7">
@@ -5379,12 +5349,12 @@
       <c r="C96" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D96" s="24" t="s">
+      <c r="D96" s="25" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="22">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="23">
         <v>45756</v>
       </c>
       <c r="B97" s="7">
@@ -5393,12 +5363,12 @@
       <c r="C97" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D97" s="24" t="s">
+      <c r="D97" s="25" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="22">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="23">
         <v>45757</v>
       </c>
       <c r="B98" s="7">
@@ -5407,12 +5377,12 @@
       <c r="C98" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D98" s="24" t="s">
+      <c r="D98" s="25" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="22">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="23">
         <v>45758</v>
       </c>
       <c r="B99" s="7">
@@ -5421,12 +5391,12 @@
       <c r="C99" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D99" s="24" t="s">
+      <c r="D99" s="25" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="22">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="23">
         <v>45759</v>
       </c>
       <c r="B100" s="7">
@@ -5435,12 +5405,12 @@
       <c r="C100" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D100" s="24" t="s">
+      <c r="D100" s="25" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="22">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="23">
         <v>45760</v>
       </c>
       <c r="B101" s="7">
@@ -5449,12 +5419,12 @@
       <c r="C101" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D101" s="24" t="s">
+      <c r="D101" s="25" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="22">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="23">
         <v>45791</v>
       </c>
       <c r="B102" s="7">
@@ -5463,12 +5433,12 @@
       <c r="C102" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D102" s="24" t="s">
+      <c r="D102" s="25" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="22">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="23">
         <v>45762</v>
       </c>
       <c r="B103" s="7">
@@ -5477,12 +5447,12 @@
       <c r="C103" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D103" s="24" t="s">
+      <c r="D103" s="25" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="22">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="23">
         <v>45763</v>
       </c>
       <c r="B104" s="7">
@@ -5491,12 +5461,12 @@
       <c r="C104" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D104" s="24" t="s">
+      <c r="D104" s="25" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="22">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="23">
         <v>45764</v>
       </c>
       <c r="B105" s="7">
@@ -5505,12 +5475,12 @@
       <c r="C105" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D105" s="24" t="s">
+      <c r="D105" s="25" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="22">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="23">
         <v>45765</v>
       </c>
       <c r="B106" s="7">
@@ -5519,12 +5489,12 @@
       <c r="C106" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D106" s="24" t="s">
+      <c r="D106" s="25" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="22">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="23">
         <v>45766</v>
       </c>
       <c r="B107" s="7">
@@ -5533,12 +5503,12 @@
       <c r="C107" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D107" s="24" t="s">
+      <c r="D107" s="25" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="22">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="23">
         <v>45767</v>
       </c>
       <c r="B108" s="7">
@@ -5547,12 +5517,12 @@
       <c r="C108" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D108" s="24" t="s">
+      <c r="D108" s="25" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="22">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="23">
         <v>45768</v>
       </c>
       <c r="B109" s="7">
@@ -5561,12 +5531,12 @@
       <c r="C109" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D109" s="24" t="s">
+      <c r="D109" s="25" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="22">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="23">
         <v>45769</v>
       </c>
       <c r="B110" s="7">
@@ -5575,12 +5545,12 @@
       <c r="C110" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D110" s="24" t="s">
+      <c r="D110" s="25" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="22">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="23">
         <v>45770</v>
       </c>
       <c r="B111" s="7">
@@ -5589,12 +5559,12 @@
       <c r="C111" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D111" s="24" t="s">
+      <c r="D111" s="25" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="22">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="23">
         <v>45771</v>
       </c>
       <c r="B112" s="7">
@@ -5603,12 +5573,12 @@
       <c r="C112" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D112" s="24" t="s">
+      <c r="D112" s="25" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="22">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="23">
         <v>45772</v>
       </c>
       <c r="B113" s="7">
@@ -5617,12 +5587,12 @@
       <c r="C113" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D113" s="24" t="s">
+      <c r="D113" s="25" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="22">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="23">
         <v>45773</v>
       </c>
       <c r="B114" s="7">
@@ -5631,12 +5601,12 @@
       <c r="C114" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D114" s="24" t="s">
+      <c r="D114" s="25" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="22">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="23">
         <v>45774</v>
       </c>
       <c r="B115" s="7">
@@ -5645,12 +5615,12 @@
       <c r="C115" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D115" s="24" t="s">
+      <c r="D115" s="25" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="22">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="23">
         <v>45775</v>
       </c>
       <c r="B116" s="7">
@@ -5659,12 +5629,12 @@
       <c r="C116" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D116" s="24" t="s">
+      <c r="D116" s="25" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="22">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="23">
         <v>45810</v>
       </c>
       <c r="B117" s="7">
@@ -5673,12 +5643,12 @@
       <c r="C117" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D117" s="24" t="s">
+      <c r="D117" s="25" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="22">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="23">
         <v>45811</v>
       </c>
       <c r="B118" s="7">
@@ -5687,12 +5657,12 @@
       <c r="C118" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D118" s="24" t="s">
+      <c r="D118" s="25" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="22">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="23">
         <v>45812</v>
       </c>
       <c r="B119" s="7">
@@ -5701,12 +5671,12 @@
       <c r="C119" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D119" s="24" t="s">
+      <c r="D119" s="25" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="22">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="23">
         <v>45813</v>
       </c>
       <c r="B120" s="7">
@@ -5715,12 +5685,12 @@
       <c r="C120" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D120" s="24" t="s">
+      <c r="D120" s="25" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="22">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="23">
         <v>45814</v>
       </c>
       <c r="B121" s="7">
@@ -5729,12 +5699,12 @@
       <c r="C121" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D121" s="24" t="s">
+      <c r="D121" s="25" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="22">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="23">
         <v>45815</v>
       </c>
       <c r="B122" s="7">
@@ -5743,12 +5713,12 @@
       <c r="C122" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D122" s="24" t="s">
+      <c r="D122" s="25" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="22">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="23">
         <v>45816</v>
       </c>
       <c r="B123" s="7">
@@ -5757,12 +5727,12 @@
       <c r="C123" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D123" s="24" t="s">
+      <c r="D123" s="25" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="22">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="23">
         <v>45817</v>
       </c>
       <c r="B124" s="7">
@@ -5771,12 +5741,12 @@
       <c r="C124" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D124" s="24" t="s">
+      <c r="D124" s="25" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="22">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="23">
         <v>45818</v>
       </c>
       <c r="B125" s="7">
@@ -5785,12 +5755,12 @@
       <c r="C125" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D125" s="24" t="s">
+      <c r="D125" s="25" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="22">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="23">
         <v>45819</v>
       </c>
       <c r="B126" s="7">
@@ -5799,12 +5769,12 @@
       <c r="C126" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D126" s="24" t="s">
+      <c r="D126" s="25" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="22">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="23">
         <v>45820</v>
       </c>
       <c r="B127" s="7">
@@ -5813,12 +5783,12 @@
       <c r="C127" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D127" s="24" t="s">
+      <c r="D127" s="25" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="22">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="23">
         <v>45821</v>
       </c>
       <c r="B128" s="7">
@@ -5827,12 +5797,12 @@
       <c r="C128" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D128" s="24" t="s">
+      <c r="D128" s="25" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="22">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="23">
         <v>45822</v>
       </c>
       <c r="B129" s="7">
@@ -5841,12 +5811,12 @@
       <c r="C129" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D129" s="24" t="s">
+      <c r="D129" s="25" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="22">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="23">
         <v>45823</v>
       </c>
       <c r="B130" s="7">
@@ -5855,12 +5825,12 @@
       <c r="C130" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D130" s="24" t="s">
+      <c r="D130" s="25" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="22">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="23">
         <v>45824</v>
       </c>
       <c r="B131" s="7">
@@ -5869,12 +5839,12 @@
       <c r="C131" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D131" s="24" t="s">
+      <c r="D131" s="25" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="22">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="23">
         <v>45825</v>
       </c>
       <c r="B132" s="7">
@@ -5883,12 +5853,12 @@
       <c r="C132" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D132" s="24" t="s">
+      <c r="D132" s="25" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="22">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="23">
         <v>45826</v>
       </c>
       <c r="B133" s="7">
@@ -5897,12 +5867,12 @@
       <c r="C133" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D133" s="24" t="s">
+      <c r="D133" s="25" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="22">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="23">
         <v>45827</v>
       </c>
       <c r="B134" s="7">
@@ -5911,12 +5881,12 @@
       <c r="C134" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D134" s="24" t="s">
+      <c r="D134" s="25" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="22">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="23">
         <v>45828</v>
       </c>
       <c r="B135" s="7">
@@ -5925,12 +5895,12 @@
       <c r="C135" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D135" s="24" t="s">
+      <c r="D135" s="25" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="22">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="23">
         <v>45829</v>
       </c>
       <c r="B136" s="7">
@@ -5939,12 +5909,12 @@
       <c r="C136" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D136" s="24" t="s">
+      <c r="D136" s="25" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="22">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="23">
         <v>45830</v>
       </c>
       <c r="B137" s="7">
@@ -5953,12 +5923,12 @@
       <c r="C137" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D137" s="24" t="s">
+      <c r="D137" s="25" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="22">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="23">
         <v>45831</v>
       </c>
       <c r="B138" s="7">
@@ -5967,12 +5937,12 @@
       <c r="C138" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D138" s="24" t="s">
+      <c r="D138" s="25" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="22">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="23">
         <v>45832</v>
       </c>
       <c r="B139" s="7">
@@ -5981,12 +5951,12 @@
       <c r="C139" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D139" s="24" t="s">
+      <c r="D139" s="25" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="22">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="23">
         <v>45833</v>
       </c>
       <c r="B140" s="7">
@@ -5995,12 +5965,12 @@
       <c r="C140" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D140" s="24" t="s">
+      <c r="D140" s="25" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="22">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="23">
         <v>45834</v>
       </c>
       <c r="B141" s="7">
@@ -6009,12 +5979,12 @@
       <c r="C141" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D141" s="24" t="s">
+      <c r="D141" s="25" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="22">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="23">
         <v>45835</v>
       </c>
       <c r="B142" s="7">
@@ -6023,12 +5993,12 @@
       <c r="C142" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D142" s="24" t="s">
+      <c r="D142" s="25" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="22">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="23">
         <v>45836</v>
       </c>
       <c r="B143" s="7">
@@ -6037,12 +6007,12 @@
       <c r="C143" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D143" s="24" t="s">
+      <c r="D143" s="25" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="22">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="23">
         <v>45837</v>
       </c>
       <c r="B144" s="7">
@@ -6051,12 +6021,12 @@
       <c r="C144" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D144" s="24" t="s">
+      <c r="D144" s="25" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="22">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="23">
         <v>45838</v>
       </c>
       <c r="B145" s="7">
@@ -6065,12 +6035,12 @@
       <c r="C145" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D145" s="24" t="s">
+      <c r="D145" s="25" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="22">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="23">
         <v>45839</v>
       </c>
       <c r="B146" s="7">
@@ -6079,12 +6049,12 @@
       <c r="C146" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D146" s="24" t="s">
+      <c r="D146" s="25" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="22">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="23">
         <v>45840</v>
       </c>
       <c r="B147" s="7">
@@ -6093,12 +6063,12 @@
       <c r="C147" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D147" s="24" t="s">
+      <c r="D147" s="25" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" s="22">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="23">
         <v>45841</v>
       </c>
       <c r="B148" s="7">
@@ -6107,12 +6077,12 @@
       <c r="C148" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D148" s="24" t="s">
+      <c r="D148" s="25" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="22">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="23">
         <v>45842</v>
       </c>
       <c r="B149" s="7">
@@ -6121,12 +6091,12 @@
       <c r="C149" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D149" s="24" t="s">
+      <c r="D149" s="25" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="22">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="23">
         <v>45843</v>
       </c>
       <c r="B150" s="7">
@@ -6135,12 +6105,12 @@
       <c r="C150" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D150" s="24" t="s">
+      <c r="D150" s="25" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="22">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="23">
         <v>45844</v>
       </c>
       <c r="B151" s="7">
@@ -6149,12 +6119,12 @@
       <c r="C151" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D151" s="24" t="s">
+      <c r="D151" s="25" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" s="22">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="23">
         <v>45845</v>
       </c>
       <c r="B152" s="7">
@@ -6163,12 +6133,12 @@
       <c r="C152" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D152" s="24" t="s">
+      <c r="D152" s="25" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" s="22">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="23">
         <v>45846</v>
       </c>
       <c r="B153" s="7">
@@ -6177,12 +6147,12 @@
       <c r="C153" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D153" s="24" t="s">
+      <c r="D153" s="25" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="22">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="23">
         <v>45847</v>
       </c>
       <c r="B154" s="7">
@@ -6191,12 +6161,12 @@
       <c r="C154" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D154" s="24" t="s">
+      <c r="D154" s="25" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="22">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="23">
         <v>45848</v>
       </c>
       <c r="B155" s="7">
@@ -6205,12 +6175,12 @@
       <c r="C155" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D155" s="24" t="s">
+      <c r="D155" s="25" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="22">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="23">
         <v>45849</v>
       </c>
       <c r="B156" s="7">
@@ -6219,12 +6189,12 @@
       <c r="C156" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D156" s="24" t="s">
+      <c r="D156" s="25" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="22">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="23">
         <v>45850</v>
       </c>
       <c r="B157" s="7">
@@ -6233,12 +6203,12 @@
       <c r="C157" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D157" s="24" t="s">
+      <c r="D157" s="25" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="22">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="23">
         <v>45851</v>
       </c>
       <c r="B158" s="7">
@@ -6247,12 +6217,12 @@
       <c r="C158" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D158" s="24" t="s">
+      <c r="D158" s="25" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="22">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="23">
         <v>45852</v>
       </c>
       <c r="B159" s="7">
@@ -6261,12 +6231,12 @@
       <c r="C159" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D159" s="24" t="s">
+      <c r="D159" s="25" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="22">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="23">
         <v>45853</v>
       </c>
       <c r="B160" s="7">
@@ -6275,12 +6245,12 @@
       <c r="C160" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D160" s="24" t="s">
+      <c r="D160" s="25" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="22">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="23">
         <v>45854</v>
       </c>
       <c r="B161" s="7">
@@ -6289,12 +6259,12 @@
       <c r="C161" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D161" s="24" t="s">
+      <c r="D161" s="25" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="22">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="23">
         <v>45855</v>
       </c>
       <c r="B162" s="7">
@@ -6303,12 +6273,12 @@
       <c r="C162" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D162" s="24" t="s">
+      <c r="D162" s="25" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="22">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="23">
         <v>45856</v>
       </c>
       <c r="B163" s="7">
@@ -6317,12 +6287,12 @@
       <c r="C163" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D163" s="24" t="s">
+      <c r="D163" s="25" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" s="22">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="23">
         <v>45857</v>
       </c>
       <c r="B164" s="7">
@@ -6331,12 +6301,12 @@
       <c r="C164" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D164" s="24" t="s">
+      <c r="D164" s="25" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="22">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="23">
         <v>45858</v>
       </c>
       <c r="B165" s="7">
@@ -6345,12 +6315,12 @@
       <c r="C165" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D165" s="24" t="s">
+      <c r="D165" s="25" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="22">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="23">
         <v>45859</v>
       </c>
       <c r="B166" s="7">
@@ -6359,12 +6329,12 @@
       <c r="C166" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D166" s="24" t="s">
+      <c r="D166" s="25" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="22">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="23">
         <v>45860</v>
       </c>
       <c r="B167" s="7">
@@ -6373,12 +6343,12 @@
       <c r="C167" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D167" s="24" t="s">
+      <c r="D167" s="25" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="22">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="23">
         <v>45861</v>
       </c>
       <c r="B168" s="7">
@@ -6387,12 +6357,12 @@
       <c r="C168" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D168" s="24" t="s">
+      <c r="D168" s="25" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="22">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="23">
         <v>45862</v>
       </c>
       <c r="B169" s="7">
@@ -6401,12 +6371,12 @@
       <c r="C169" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D169" s="24" t="s">
+      <c r="D169" s="25" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="22">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="23">
         <v>45863</v>
       </c>
       <c r="B170" s="7">
@@ -6415,12 +6385,12 @@
       <c r="C170" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D170" s="24" t="s">
+      <c r="D170" s="25" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="22">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="23">
         <v>45864</v>
       </c>
       <c r="B171" s="7">
@@ -6429,12 +6399,12 @@
       <c r="C171" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D171" s="24" t="s">
+      <c r="D171" s="25" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="22">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="23">
         <v>45865</v>
       </c>
       <c r="B172" s="7">
@@ -6443,12 +6413,12 @@
       <c r="C172" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D172" s="24" t="s">
+      <c r="D172" s="25" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="22">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="23">
         <v>45866</v>
       </c>
       <c r="B173" s="7">
@@ -6457,12 +6427,12 @@
       <c r="C173" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D173" s="24" t="s">
+      <c r="D173" s="25" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="22">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="23">
         <v>45867</v>
       </c>
       <c r="B174" s="7">
@@ -6471,12 +6441,12 @@
       <c r="C174" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D174" s="24" t="s">
+      <c r="D174" s="25" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="22">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="23">
         <v>45868</v>
       </c>
       <c r="B175" s="7">
@@ -6485,12 +6455,12 @@
       <c r="C175" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D175" s="24" t="s">
+      <c r="D175" s="25" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="22">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="23">
         <v>45870</v>
       </c>
       <c r="B176" s="7">
@@ -6499,12 +6469,12 @@
       <c r="C176" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D176" s="24" t="s">
+      <c r="D176" s="25" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="22">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="23">
         <v>45871</v>
       </c>
       <c r="B177" s="7">
@@ -6513,12 +6483,12 @@
       <c r="C177" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D177" s="24" t="s">
+      <c r="D177" s="25" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="22">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="23">
         <v>45872</v>
       </c>
       <c r="B178" s="7">
@@ -6527,12 +6497,12 @@
       <c r="C178" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D178" s="24" t="s">
+      <c r="D178" s="25" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="22">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="23">
         <v>45873</v>
       </c>
       <c r="B179" s="7">
@@ -6541,12 +6511,12 @@
       <c r="C179" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D179" s="24" t="s">
+      <c r="D179" s="25" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="22">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="23">
         <v>45874</v>
       </c>
       <c r="B180" s="7">
@@ -6555,12 +6525,12 @@
       <c r="C180" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D180" s="24" t="s">
+      <c r="D180" s="25" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="22">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="23">
         <v>45875</v>
       </c>
       <c r="B181" s="7">
@@ -6569,12 +6539,12 @@
       <c r="C181" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D181" s="24" t="s">
+      <c r="D181" s="25" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="22">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="23">
         <v>45876</v>
       </c>
       <c r="B182" s="7">
@@ -6583,12 +6553,12 @@
       <c r="C182" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D182" s="24" t="s">
+      <c r="D182" s="25" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="22">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="23">
         <v>45877</v>
       </c>
       <c r="B183" s="7">
@@ -6597,12 +6567,12 @@
       <c r="C183" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D183" s="24" t="s">
+      <c r="D183" s="25" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="22">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="23">
         <v>45878</v>
       </c>
       <c r="B184" s="7">
@@ -6611,12 +6581,12 @@
       <c r="C184" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D184" s="24" t="s">
+      <c r="D184" s="25" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="22">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="23">
         <v>45879</v>
       </c>
       <c r="B185" s="7">
@@ -6625,12 +6595,12 @@
       <c r="C185" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D185" s="24" t="s">
+      <c r="D185" s="25" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="22">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="23">
         <v>45880</v>
       </c>
       <c r="B186" s="7">
@@ -6639,12 +6609,12 @@
       <c r="C186" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D186" s="24" t="s">
+      <c r="D186" s="25" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="22">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="23">
         <v>45881</v>
       </c>
       <c r="B187" s="7">
@@ -6653,12 +6623,12 @@
       <c r="C187" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D187" s="24" t="s">
+      <c r="D187" s="25" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="22">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" s="23">
         <v>45882</v>
       </c>
       <c r="B188" s="7">
@@ -6667,12 +6637,12 @@
       <c r="C188" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D188" s="24" t="s">
+      <c r="D188" s="25" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="22">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" s="23">
         <v>45883</v>
       </c>
       <c r="B189" s="7">
@@ -6681,12 +6651,12 @@
       <c r="C189" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D189" s="24" t="s">
+      <c r="D189" s="25" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="22">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" s="23">
         <v>45884</v>
       </c>
       <c r="B190" s="7">
@@ -6695,12 +6665,12 @@
       <c r="C190" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D190" s="24" t="s">
+      <c r="D190" s="25" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="22">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" s="23">
         <v>45885</v>
       </c>
       <c r="B191" s="7">
@@ -6709,12 +6679,12 @@
       <c r="C191" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D191" s="24" t="s">
+      <c r="D191" s="25" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="22">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" s="23">
         <v>45886</v>
       </c>
       <c r="B192" s="7">
@@ -6723,12 +6693,12 @@
       <c r="C192" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D192" s="24" t="s">
+      <c r="D192" s="25" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" s="22">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193" s="23">
         <v>45887</v>
       </c>
       <c r="B193" s="7">
@@ -6737,12 +6707,12 @@
       <c r="C193" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D193" s="24" t="s">
+      <c r="D193" s="25" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="22">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194" s="23">
         <v>45888</v>
       </c>
       <c r="B194" s="7">
@@ -6751,12 +6721,12 @@
       <c r="C194" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D194" s="24" t="s">
+      <c r="D194" s="25" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="22">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" s="23">
         <v>45889</v>
       </c>
       <c r="B195" s="7">
@@ -6765,12 +6735,12 @@
       <c r="C195" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D195" s="24" t="s">
+      <c r="D195" s="25" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" s="22">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="23">
         <v>45890</v>
       </c>
       <c r="B196" s="7">
@@ -6779,12 +6749,12 @@
       <c r="C196" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D196" s="24" t="s">
+      <c r="D196" s="25" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="22">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" s="23">
         <v>45891</v>
       </c>
       <c r="B197" s="7">
@@ -6793,12 +6763,12 @@
       <c r="C197" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D197" s="24" t="s">
+      <c r="D197" s="25" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="22">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" s="23">
         <v>45892</v>
       </c>
       <c r="B198" s="7">
@@ -6807,12 +6777,12 @@
       <c r="C198" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D198" s="24" t="s">
+      <c r="D198" s="25" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="22">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" s="23">
         <v>45893</v>
       </c>
       <c r="B199" s="7">
@@ -6821,12 +6791,12 @@
       <c r="C199" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D199" s="24" t="s">
+      <c r="D199" s="25" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" s="22">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" s="23">
         <v>45894</v>
       </c>
       <c r="B200" s="7">
@@ -6835,12 +6805,12 @@
       <c r="C200" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D200" s="24" t="s">
+      <c r="D200" s="25" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="22">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" s="23">
         <v>45895</v>
       </c>
       <c r="B201" s="7">
@@ -6849,12 +6819,12 @@
       <c r="C201" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D201" s="24" t="s">
+      <c r="D201" s="25" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" s="22">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" s="23">
         <v>45896</v>
       </c>
       <c r="B202" s="7">
@@ -6863,12 +6833,12 @@
       <c r="C202" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D202" s="24" t="s">
+      <c r="D202" s="25" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A203" s="22">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203" s="23">
         <v>45897</v>
       </c>
       <c r="B203" s="7">
@@ -6877,12 +6847,12 @@
       <c r="C203" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D203" s="24" t="s">
+      <c r="D203" s="25" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" s="22">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A204" s="23">
         <v>45898</v>
       </c>
       <c r="B204" s="7">
@@ -6891,12 +6861,12 @@
       <c r="C204" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D204" s="24" t="s">
+      <c r="D204" s="25" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" s="22">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A205" s="23">
         <v>45899</v>
       </c>
       <c r="B205" s="7">
@@ -6905,12 +6875,12 @@
       <c r="C205" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D205" s="24" t="s">
+      <c r="D205" s="25" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" s="22">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A206" s="23">
         <v>45900</v>
       </c>
       <c r="B206" s="7">
@@ -6919,12 +6889,12 @@
       <c r="C206" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D206" s="24" t="s">
+      <c r="D206" s="25" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A207" s="22">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A207" s="23">
         <v>45901</v>
       </c>
       <c r="B207" s="7">
@@ -6933,12 +6903,12 @@
       <c r="C207" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D207" s="24" t="s">
+      <c r="D207" s="25" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A208" s="22">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A208" s="23">
         <v>45902</v>
       </c>
       <c r="B208" s="7">
@@ -6947,12 +6917,12 @@
       <c r="C208" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D208" s="24" t="s">
+      <c r="D208" s="25" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" s="22">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" s="23">
         <v>45903</v>
       </c>
       <c r="B209" s="7">
@@ -6961,12 +6931,12 @@
       <c r="C209" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D209" s="24" t="s">
+      <c r="D209" s="25" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" s="22">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210" s="23">
         <v>45904</v>
       </c>
       <c r="B210" s="7">
@@ -6975,12 +6945,12 @@
       <c r="C210" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D210" s="24" t="s">
+      <c r="D210" s="25" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" s="22">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A211" s="23">
         <v>45905</v>
       </c>
       <c r="B211" s="7">
@@ -6989,12 +6959,12 @@
       <c r="C211" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D211" s="24" t="s">
+      <c r="D211" s="25" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A212" s="22">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A212" s="23">
         <v>45906</v>
       </c>
       <c r="B212" s="7">
@@ -7003,12 +6973,12 @@
       <c r="C212" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D212" s="24" t="s">
+      <c r="D212" s="25" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A213" s="22">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A213" s="23">
         <v>45907</v>
       </c>
       <c r="B213" s="7">
@@ -7017,12 +6987,12 @@
       <c r="C213" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D213" s="24" t="s">
+      <c r="D213" s="25" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" s="22">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A214" s="23">
         <v>45908</v>
       </c>
       <c r="B214" s="7">
@@ -7031,12 +7001,12 @@
       <c r="C214" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D214" s="24" t="s">
+      <c r="D214" s="25" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="22">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A215" s="23">
         <v>45909</v>
       </c>
       <c r="B215" s="7">
@@ -7045,12 +7015,12 @@
       <c r="C215" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D215" s="24" t="s">
+      <c r="D215" s="25" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A216" s="22">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A216" s="23">
         <v>45910</v>
       </c>
       <c r="B216" s="7">
@@ -7059,12 +7029,12 @@
       <c r="C216" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D216" s="24" t="s">
+      <c r="D216" s="25" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A217" s="22">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A217" s="23">
         <v>45911</v>
       </c>
       <c r="B217" s="7">
@@ -7073,12 +7043,12 @@
       <c r="C217" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D217" s="24" t="s">
+      <c r="D217" s="25" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A218" s="22">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A218" s="23">
         <v>45912</v>
       </c>
       <c r="B218" s="7">
@@ -7087,12 +7057,12 @@
       <c r="C218" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D218" s="24" t="s">
+      <c r="D218" s="25" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A219" s="22">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A219" s="23">
         <v>45913</v>
       </c>
       <c r="B219" s="7">
@@ -7101,12 +7071,12 @@
       <c r="C219" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D219" s="24" t="s">
+      <c r="D219" s="25" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A220" s="22">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A220" s="23">
         <v>45914</v>
       </c>
       <c r="B220" s="7">
@@ -7115,12 +7085,12 @@
       <c r="C220" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D220" s="24" t="s">
+      <c r="D220" s="25" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A221" s="22">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A221" s="23">
         <v>45915</v>
       </c>
       <c r="B221" s="7">
@@ -7129,12 +7099,12 @@
       <c r="C221" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D221" s="24" t="s">
+      <c r="D221" s="25" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" s="22">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A222" s="23">
         <v>45916</v>
       </c>
       <c r="B222" s="7">
@@ -7143,12 +7113,12 @@
       <c r="C222" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D222" s="24" t="s">
+      <c r="D222" s="25" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" s="22">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A223" s="23">
         <v>45917</v>
       </c>
       <c r="B223" s="7">
@@ -7157,12 +7127,12 @@
       <c r="C223" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D223" s="24" t="s">
+      <c r="D223" s="25" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A224" s="22">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A224" s="23">
         <v>45918</v>
       </c>
       <c r="B224" s="7">
@@ -7171,12 +7141,12 @@
       <c r="C224" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D224" s="24" t="s">
+      <c r="D224" s="25" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A225" s="22">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225" s="23">
         <v>45919</v>
       </c>
       <c r="B225" s="7">
@@ -7185,12 +7155,12 @@
       <c r="C225" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D225" s="24" t="s">
+      <c r="D225" s="25" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A226" s="22">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A226" s="23">
         <v>45920</v>
       </c>
       <c r="B226" s="7">
@@ -7199,12 +7169,12 @@
       <c r="C226" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D226" s="24" t="s">
+      <c r="D226" s="25" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A227" s="22">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227" s="23">
         <v>45921</v>
       </c>
       <c r="B227" s="7">
@@ -7213,12 +7183,12 @@
       <c r="C227" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D227" s="24" t="s">
+      <c r="D227" s="25" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A228" s="22">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A228" s="23">
         <v>45922</v>
       </c>
       <c r="B228" s="7">
@@ -7227,12 +7197,12 @@
       <c r="C228" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D228" s="24" t="s">
+      <c r="D228" s="25" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A229" s="22">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229" s="23">
         <v>45923</v>
       </c>
       <c r="B229" s="7">
@@ -7241,12 +7211,12 @@
       <c r="C229" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D229" s="24" t="s">
+      <c r="D229" s="25" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A230" s="22">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230" s="23">
         <v>45924</v>
       </c>
       <c r="B230" s="7">
@@ -7255,12 +7225,12 @@
       <c r="C230" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D230" s="24" t="s">
+      <c r="D230" s="25" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A231" s="22">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231" s="23">
         <v>45925</v>
       </c>
       <c r="B231" s="7">
@@ -7269,12 +7239,12 @@
       <c r="C231" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D231" s="24" t="s">
+      <c r="D231" s="25" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A232" s="22">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232" s="23">
         <v>45926</v>
       </c>
       <c r="B232" s="7">
@@ -7283,12 +7253,12 @@
       <c r="C232" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D232" s="24" t="s">
+      <c r="D232" s="25" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A233" s="22">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233" s="23">
         <v>45927</v>
       </c>
       <c r="B233" s="7">
@@ -7297,12 +7267,12 @@
       <c r="C233" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D233" s="24" t="s">
+      <c r="D233" s="25" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A234" s="22">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234" s="23">
         <v>45928</v>
       </c>
       <c r="B234" s="7">
@@ -7311,12 +7281,12 @@
       <c r="C234" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D234" s="24" t="s">
+      <c r="D234" s="25" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A235" s="22">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235" s="23">
         <v>45929</v>
       </c>
       <c r="B235" s="7">
@@ -7325,12 +7295,12 @@
       <c r="C235" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D235" s="24" t="s">
+      <c r="D235" s="25" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A236" s="22">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236" s="23">
         <v>45930</v>
       </c>
       <c r="B236" s="7">
@@ -7339,7 +7309,7 @@
       <c r="C236" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D236" s="24" t="s">
+      <c r="D236" s="25" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7352,87 +7322,87 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="12" width="8.85546875" style="14" customWidth="1"/>
-    <col min="13" max="16384" width="8.85546875" style="14"/>
+    <col min="1" max="1" width="6.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="8.88671875" style="15" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="20" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="16">
         <v>1603</v>
       </c>
-      <c r="B2" s="16" t="str">
+      <c r="B2" s="17" t="str">
         <f>IF(VALUE(RIGHT(A2,2))&lt;=25,"BLOCK A","BLOCK B")</f>
         <v>BLOCK A</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="18">
         <v>45927</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="B3" s="16" t="str">
+      <c r="B3" s="17" t="str">
         <f>IF(VALUE(RIGHT(A3,2))&lt;=25,"BLOCK A","BLOCK B")</f>
         <v>BLOCK A</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="18">
         <v>45929</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>398</v>
       </c>
-      <c r="B4" s="16" t="str">
+      <c r="B4" s="17" t="str">
         <f>IF(VALUE(RIGHT(A4,2))&lt;=25,"BLOCK A","BLOCK B")</f>
         <v>BLOCK A</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="18">
         <v>45929</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="B5" s="16" t="str">
+      <c r="B5" s="17" t="str">
         <f>IF(VALUE(RIGHT(A5,2))&lt;=25,"BLOCK A","BLOCK B")</f>
         <v>BLOCK A</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <v>45930</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>401</v>
       </c>
     </row>
@@ -7445,15 +7415,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" style="6" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" style="6" customWidth="1"/>
-    <col min="3" max="25" width="8.85546875" style="6" customWidth="1"/>
-    <col min="26" max="16384" width="8.85546875" style="6"/>
+    <col min="2" max="2" width="22.44140625" style="6" customWidth="1"/>
+    <col min="3" max="24" width="8.88671875" style="6" customWidth="1"/>
+    <col min="25" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>392</v>
       </c>
@@ -7461,7 +7431,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>403</v>
       </c>
@@ -7469,7 +7439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>404</v>
       </c>
@@ -7477,7 +7447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>405</v>
       </c>
@@ -7485,7 +7455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>406</v>
       </c>
@@ -7493,7 +7463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>407</v>
       </c>
@@ -7501,7 +7471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>408</v>
       </c>
@@ -7518,17 +7488,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="10" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>410</v>
       </c>
@@ -7542,72 +7512,72 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>423</v>
       </c>
@@ -7615,7 +7585,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>425</v>
       </c>
@@ -7623,137 +7593,137 @@
         <v>424</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>452</v>
       </c>
@@ -7766,296 +7736,298 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="27" width="8.85546875" style="6" customWidth="1"/>
-    <col min="28" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="37" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="27.88671875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="22.109375" style="14" customWidth="1"/>
+    <col min="11" max="26" width="8.88671875" style="6" customWidth="1"/>
+    <col min="27" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="19" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
-        <v>451</v>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>452</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="F2" s="4">
-        <v>14</v>
-      </c>
-      <c r="G2" s="4">
+        <v>468</v>
+      </c>
+      <c r="F2" s="5">
+        <v>19</v>
+      </c>
+      <c r="G2" s="5">
+        <v>9</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="F3" s="5">
+        <v>82</v>
+      </c>
+      <c r="G3" s="5">
+        <v>41</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="F4" s="5">
+        <v>69</v>
+      </c>
+      <c r="G4" s="5">
+        <v>38</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="F5" s="5">
+        <v>9</v>
+      </c>
+      <c r="G5" s="5">
+        <v>28</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J5" s="19"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="F6" s="5">
+        <v>202</v>
+      </c>
+      <c r="G6" s="5">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="18"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>452</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="H6" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="F3" s="5">
-        <v>19</v>
-      </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J3" s="18"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>450</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="F7" s="5">
+        <v>23</v>
+      </c>
+      <c r="G7" s="5">
+        <v>26</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="F4" s="5">
-        <v>84</v>
-      </c>
-      <c r="G4" s="5">
-        <v>44</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>449</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="F5" s="5">
-        <v>69</v>
-      </c>
-      <c r="G5" s="5">
-        <v>42</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J5" s="18"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>448</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="F6" s="5">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5">
-        <v>29</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F7" s="5">
-        <v>217</v>
-      </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J7" s="18"/>
+      <c r="J7" s="19"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>445</v>
+      <c r="A8" s="19" t="s">
+        <v>443</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>494</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>496</v>
       </c>
       <c r="F8" s="5">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G8" s="5">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J8" s="19"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>500</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>500</v>
       </c>
       <c r="F9" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>501</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J9" s="18"/>
+        <v>476</v>
+      </c>
+      <c r="J9" s="19"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>442</v>
+      <c r="A10" s="19" t="s">
+        <v>441</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>502</v>
@@ -8067,415 +8039,415 @@
         <v>504</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="F10" s="5">
+        <v>17</v>
+      </c>
+      <c r="G10" s="5">
+        <v>49</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="F10" s="5">
-        <v>5</v>
-      </c>
-      <c r="G10" s="5">
-        <v>8</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J10" s="19"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>441</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>13</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="I11" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J11" s="19"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F11" s="5">
-        <v>20</v>
-      </c>
-      <c r="G11" s="5">
-        <v>52</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J11" s="18"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>440</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="E12" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6</v>
+      </c>
+      <c r="G12" s="5">
+        <v>15</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="F12" s="5">
-        <v>2</v>
-      </c>
-      <c r="G12" s="5">
-        <v>13</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="J12" s="19"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="E13" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="F13" s="5">
+        <v>36</v>
+      </c>
+      <c r="G13" s="5">
+        <v>34</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="F13" s="5">
-        <v>6</v>
-      </c>
-      <c r="G13" s="5">
-        <v>15</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>438</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>517</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>494</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>518</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F14" s="5">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G14" s="5">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>478</v>
+        <v>520</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J14" s="18"/>
+        <v>476</v>
+      </c>
+      <c r="J14" s="19"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>437</v>
+      <c r="A15" s="19" t="s">
+        <v>436</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F15" s="5">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G15" s="5">
+        <v>23</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J15" s="19"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="F16" s="5">
         <v>5</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
-        <v>436</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="F16" s="5">
+      <c r="G16" s="5">
         <v>17</v>
       </c>
-      <c r="G16" s="5">
-        <v>27</v>
-      </c>
       <c r="H16" s="5" t="s">
-        <v>527</v>
+        <v>475</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J16" s="18"/>
+        <v>470</v>
+      </c>
+      <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>435</v>
+      <c r="A17" s="19" t="s">
+        <v>433</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F17" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G17" s="5">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J17" s="18"/>
+        <v>476</v>
+      </c>
+      <c r="J17" s="19"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
-        <v>433</v>
+      <c r="A18" s="19" t="s">
+        <v>429</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>534</v>
+        <v>500</v>
       </c>
       <c r="F18" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G18" s="5">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J18" s="18"/>
+        <v>476</v>
+      </c>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>429</v>
+      <c r="A19" s="19" t="s">
+        <v>428</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="F19" s="5">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G19" s="5">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>538</v>
+        <v>475</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J19" s="18"/>
+        <v>476</v>
+      </c>
+      <c r="J19" s="19"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>428</v>
+      <c r="A20" s="19" t="s">
+        <v>420</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>541</v>
+        <v>503</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F20" s="5">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G20" s="5">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J20" s="18"/>
+        <v>470</v>
+      </c>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
-        <v>420</v>
+      <c r="A21" s="19" t="s">
+        <v>432</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>544</v>
+        <v>503</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>545</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="F21" s="5">
+        <v>44</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="J21" s="19"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="F21" s="5">
-        <v>17</v>
-      </c>
-      <c r="G21" s="5">
-        <v>9</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="C22" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
-        <v>432</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="F22" s="5">
+        <v>5</v>
+      </c>
+      <c r="G22" s="5">
+        <v>103</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J22" s="19"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="F22" s="5">
-        <v>46</v>
-      </c>
-      <c r="G22" s="5">
-        <v>2</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
-        <v>431</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="F23" s="5">
+        <v>79</v>
+      </c>
+      <c r="G23" s="5">
+        <v>92</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J23" s="19"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
         <v>552</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="F23" s="5">
-        <v>5</v>
-      </c>
-      <c r="G23" s="5">
-        <v>111</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>417</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>553</v>
@@ -8484,264 +8456,234 @@
         <v>554</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F24" s="5">
+        <v>34</v>
+      </c>
+      <c r="G24" s="5">
+        <v>20</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="C25" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="F24" s="5">
-        <v>79</v>
-      </c>
-      <c r="G24" s="5">
-        <v>106</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="E25" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="F25" s="5">
+        <v>15</v>
+      </c>
+      <c r="G25" s="5">
+        <v>20</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="I25" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J25" s="19"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="F25" s="5">
-        <v>35</v>
-      </c>
-      <c r="G25" s="5">
-        <v>22</v>
-      </c>
-      <c r="H25" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
-        <v>430</v>
-      </c>
-      <c r="B26" s="4" t="s">
+      <c r="F26" s="5">
+        <v>33</v>
+      </c>
+      <c r="G26" s="5">
+        <v>44</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J26" s="19"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F26" s="5">
-        <v>15</v>
-      </c>
-      <c r="G26" s="5">
-        <v>20</v>
-      </c>
-      <c r="H26" s="5" t="s">
+      <c r="D27" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="F27" s="5">
+        <v>16</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
-        <v>415</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="I27" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="J27" s="19"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C28" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="E27" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="F27" s="5">
-        <v>33</v>
-      </c>
-      <c r="G27" s="5">
-        <v>49</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
-        <v>416</v>
-      </c>
-      <c r="B28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="F28" s="5">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5">
+        <v>7</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="F28" s="5">
-        <v>16</v>
-      </c>
-      <c r="G28" s="5">
-        <v>3</v>
-      </c>
-      <c r="H28" s="5" t="s">
+      <c r="I28" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J28" s="19"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
-        <v>427</v>
-      </c>
-      <c r="B29" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>573</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>560</v>
       </c>
       <c r="F29" s="5">
         <v>1</v>
       </c>
       <c r="G29" s="5">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H29" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J29" s="19"/>
+    </row>
+    <row r="30" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J29" s="18"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
-        <v>414</v>
-      </c>
-      <c r="B30" s="4" t="s">
+      <c r="C30" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="E30" s="5" t="s">
         <v>576</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>578</v>
       </c>
       <c r="F30" s="5">
         <v>1</v>
       </c>
       <c r="G30" s="5">
-        <v>52</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>478</v>
+        <v>6</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>577</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J30" s="18"/>
-    </row>
-    <row r="31" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
-        <v>413</v>
-      </c>
-      <c r="B31" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="J30" s="19"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="F31" s="5">
+      <c r="D31" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="F31" s="4">
         <v>1</v>
       </c>
-      <c r="G31" s="5">
-        <v>10</v>
-      </c>
-      <c r="H31" s="26" t="s">
-        <v>542</v>
+      <c r="G31" s="4">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>464</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J31" s="18"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
-        <v>419</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="F32" s="4">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4">
-        <v>2</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="J32" s="18"/>
+        <v>470</v>
+      </c>
+      <c r="J31" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8752,33 +8694,33 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="7" customWidth="1"/>
+    <col min="1" max="2" width="8.88671875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="B2" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8436,7 +8436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col width="37" customWidth="1" style="11" min="1" max="1"/>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8528,7 +8528,12 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>Không có dữ liệu</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8545,28 +8550,33 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>497</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8583,28 +8593,33 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>630</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9840,7 +9840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9893,17 +9893,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -9913,7 +9919,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Không có dữ liệu</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -9928,24 +9939,35 @@
           <t>603</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>496</v>
-      </c>
-      <c r="D3" t="n">
-        <v>134</v>
-      </c>
-      <c r="E3" t="n">
-        <v>128</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -9960,24 +9982,35 @@
           <t>621</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>604</v>
-      </c>
-      <c r="D4" t="n">
-        <v>356</v>
-      </c>
-      <c r="E4" t="n">
-        <v>304</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9924,7 +9924,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>04/2026</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9840,7 +9840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10014,6 +10014,1070 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>69</v>
+      </c>
+      <c r="G5" t="n">
+        <v>57</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>41</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1,139</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>253</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>23</v>
+      </c>
+      <c r="G8" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" t="n">
+        <v>53</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>31/12/2025</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G14" t="n">
+        <v>53</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>17</v>
+      </c>
+      <c r="G16" t="n">
+        <v>28</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>62</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>53</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>129</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>79</v>
+      </c>
+      <c r="G24" t="n">
+        <v>111</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>38</v>
+      </c>
+      <c r="G25" t="n">
+        <v>29</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" t="n">
+        <v>23</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>33</v>
+      </c>
+      <c r="G27" t="n">
+        <v>63</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>16</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>78</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9893,22 +9893,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -9998,10 +9998,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>253</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -10150,10 +10150,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -10264,10 +10264,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -10378,10 +10378,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -10568,10 +10568,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
         <v>9</v>
@@ -10682,7 +10682,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -10723,7 +10723,7 @@
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -10796,10 +10796,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -10872,10 +10872,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>4</v>
@@ -10989,7 +10989,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8533,7 +8533,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8650,14 +8650,19 @@
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8688,14 +8693,19 @@
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8726,14 +8736,19 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>10</v>
+        <v>253</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8764,14 +8779,19 @@
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8805,11 +8825,16 @@
         <v>7</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8843,11 +8868,16 @@
         <v>5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8878,14 +8908,19 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>31/12/2025</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8919,11 +8954,16 @@
         <v>2</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -8957,11 +8997,16 @@
         <v>6</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>13/09/2025</t>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>03/2026</t>
         </is>
       </c>
     </row>
@@ -8992,14 +9037,19 @@
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>05/09/2025</t>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9033,11 +9083,16 @@
         <v>4</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9068,14 +9123,19 @@
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>06/08/2025</t>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9109,11 +9169,16 @@
         <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9147,11 +9212,16 @@
         <v>2</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9182,14 +9252,19 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>24/03/2025</t>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9220,14 +9295,19 @@
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9258,14 +9338,19 @@
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>29/04/2025</t>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9296,14 +9381,19 @@
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>03/2026</t>
         </is>
       </c>
     </row>
@@ -9337,11 +9427,16 @@
         <v>5</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9372,14 +9467,19 @@
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>27/12/2025</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12/2025</t>
         </is>
       </c>
     </row>
@@ -9410,14 +9510,19 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>08/09/2025</t>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9448,14 +9553,19 @@
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>08/09/2025</t>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9486,14 +9596,19 @@
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9524,14 +9639,19 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>19/07/2025</t>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>03/2026</t>
         </is>
       </c>
     </row>
@@ -9565,11 +9685,16 @@
         <v>1</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>20/08/2025</t>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9603,11 +9728,16 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9641,9 +9771,18 @@
         <v>1</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="15" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -9675,9 +9814,18 @@
         <v>1</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="8" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10488,7 +10636,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F17" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8610,11 +8610,11 @@
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8653,11 +8653,11 @@
         <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8736,14 +8736,14 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8782,11 +8782,11 @@
         <v>23</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8911,11 +8911,11 @@
         <v>20</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>31/12/2025</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9040,11 +9040,11 @@
         <v>36</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9126,11 +9126,11 @@
         <v>17</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9169,11 +9169,11 @@
         <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9298,11 +9298,11 @@
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9427,11 +9427,11 @@
         <v>5</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9556,11 +9556,11 @@
         <v>15</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9728,11 +9728,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9814,16 +9814,16 @@
         <v>1</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -10041,7 +10041,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>484</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -10550,17 +10550,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -11044,17 +11044,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F28" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8521,19 +8521,19 @@
         </is>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G2" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>01/2026</t>
         </is>
       </c>
     </row>
@@ -8567,11 +8567,11 @@
         <v>19</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -8610,11 +8610,11 @@
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8653,11 +8653,11 @@
         <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8736,14 +8736,14 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8868,11 +8868,11 @@
         <v>5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>14/02/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8911,11 +8911,11 @@
         <v>20</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8997,16 +8997,16 @@
         <v>6</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>03/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
     </row>
@@ -9040,11 +9040,11 @@
         <v>36</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9083,11 +9083,11 @@
         <v>4</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9169,11 +9169,11 @@
         <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9255,11 +9255,11 @@
         <v>15</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9298,11 +9298,11 @@
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9341,11 +9341,11 @@
         <v>17</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9381,14 +9381,14 @@
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" s="10" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9427,11 +9427,11 @@
         <v>5</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9513,11 +9513,11 @@
         <v>38</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9556,11 +9556,11 @@
         <v>15</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9599,11 +9599,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9728,11 +9728,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9771,11 +9771,11 @@
         <v>1</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -10041,22 +10041,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>882</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>149</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10365,12 +10365,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -10593,12 +10593,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11006,17 +11006,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>235</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -11125,12 +11125,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -11158,17 +11158,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F31" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8533,7 +8533,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>01/2026</t>
+          <t>11/2025</t>
         </is>
       </c>
     </row>
@@ -8610,11 +8610,11 @@
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8911,11 +8911,11 @@
         <v>20</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -9427,11 +9427,11 @@
         <v>5</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9510,14 +9510,14 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9599,11 +9599,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -10041,22 +10041,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>496</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10132,17 +10132,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>632</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>397</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>325</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10593,12 +10593,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -11044,17 +11044,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -11158,17 +11158,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F31" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="429" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Login" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CanHo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="GIAM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Project" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="BaoCao" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="NoCu" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet name="DaThanhToan" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Login" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CanHo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIAM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BaoCao" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NoCu" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DaThanhToan" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$C$223</definedName>
@@ -8423,7 +8423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col width="37" customWidth="1" style="11" min="1" max="1"/>
@@ -9811,6 +9811,13 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHUNG CƯ RIVA PARK</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="429" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Login" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CanHo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIAM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BaoCao" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NoCu" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DaThanhToan" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="Login" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CanHo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GIAM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Project" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="BaoCao" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="NoCu" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="DaThanhToan" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$C$223</definedName>
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -9818,6 +9818,42 @@
       <c r="A33" t="inlineStr">
         <is>
           <t>CHUNG CƯ RIVA PARK</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>05/2026</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>511</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>398</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -8597,11 +8597,11 @@
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>485</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -9285,11 +9285,11 @@
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9822,22 +9822,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>347</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>634</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -8597,11 +8597,11 @@
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -8640,11 +8640,11 @@
         <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8714,28 +8714,28 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>501</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -8898,11 +8898,11 @@
         <v>20</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9285,11 +9285,11 @@
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -9574,23 +9574,23 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -9827,28 +9827,28 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8499,12 +8499,12 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
           <t>124</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>123</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -8597,11 +8597,11 @@
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8628,23 +8628,23 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
         <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8714,23 +8714,23 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>228</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8984,11 +8984,11 @@
         <v>6</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9027,11 +9027,11 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9113,11 +9113,11 @@
         <v>17</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9285,11 +9285,11 @@
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9586,11 +9586,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>349</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
           <t>124</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>123</t>
         </is>
       </c>
       <c r="F31" s="15" t="n">
@@ -9827,17 +9827,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>94</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -8580,28 +8580,28 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>635</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>399</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>326</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -8723,14 +8723,14 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8855,11 +8855,11 @@
         <v>5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -9027,11 +9027,11 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9113,11 +9113,11 @@
         <v>17</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
@@ -9285,11 +9285,11 @@
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -9483,17 +9483,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
@@ -9586,16 +9586,16 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>350</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -9827,28 +9827,28 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -8623,33 +8623,33 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
         <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -8723,14 +8723,14 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -8898,11 +8898,11 @@
         <v>20</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9027,16 +9027,16 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9096,12 +9096,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9586,11 +9586,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>05/2026</t>
         </is>
       </c>
     </row>
@@ -9715,16 +9715,16 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F31" s="15" t="n">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9827,17 +9827,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>511</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -8671,23 +8671,23 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
         <v>10</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8723,19 +8723,19 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -8984,11 +8984,11 @@
         <v>6</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -9027,11 +9027,11 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>201</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -9113,11 +9113,11 @@
         <v>17</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9156,16 +9156,16 @@
         <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9187,12 +9187,12 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9316,12 +9316,12 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
@@ -9368,14 +9368,14 @@
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G22" s="10" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
@@ -9500,11 +9500,11 @@
         <v>39</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9586,11 +9586,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9698,12 +9698,12 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>638</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -8597,11 +8597,11 @@
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8640,11 +8640,11 @@
         <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -9096,17 +9096,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>202</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
@@ -9698,28 +9698,28 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>352</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>265</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>511</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8580,28 +8580,28 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>639</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>402</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>327</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8640,11 +8640,11 @@
         <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8723,14 +8723,14 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9027,11 +9027,11 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
@@ -9156,11 +9156,11 @@
         <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9285,11 +9285,11 @@
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9500,11 +9500,11 @@
         <v>39</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9564,17 +9564,17 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>266</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>236</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -9586,11 +9586,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>348</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>638</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>401</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -8597,16 +8597,16 @@
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -8628,12 +8628,12 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -8709,28 +8709,28 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>486</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>229</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8812,11 +8812,11 @@
         <v>7</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>14/02/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8898,16 +8898,16 @@
         <v>20</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>203</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9230,28 +9230,28 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F19" s="10" t="n">
         <v>15</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9268,17 +9268,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9371,16 +9371,16 @@
         <v>55</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>06/2026</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>353</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -9715,16 +9715,16 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9822,12 +9822,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>331</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9844,11 +9844,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>511</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8551,19 +8551,19 @@
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -8580,28 +8580,28 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>639</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>402</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>328</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -8723,19 +8723,19 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -8812,11 +8812,11 @@
         <v>7</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9058,12 +9058,12 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F15" s="10" t="n">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9182,17 +9182,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F18" s="10" t="n">
@@ -9268,28 +9268,28 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9500,11 +9500,11 @@
         <v>39</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>27/06/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9586,11 +9586,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>354</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -9827,33 +9827,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8551,14 +8551,14 @@
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>16</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -8580,28 +8580,28 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>403</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>329</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -8709,28 +8709,28 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>492</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>231</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>507</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8812,16 +8812,16 @@
         <v>7</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -8855,11 +8855,11 @@
         <v>5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9242,11 +9242,11 @@
         <v>15</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9268,28 +9268,28 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9328,11 +9328,11 @@
         <v>17</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9414,7 +9414,7 @@
         <v>5</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
@@ -9497,14 +9497,14 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9586,11 +9586,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>355</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9844,11 +9844,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8542,23 +8542,23 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>152</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>145</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
         <v>21</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>404</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -8683,11 +8683,11 @@
         <v>10</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>232</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
@@ -8812,11 +8812,11 @@
         <v>7</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9027,11 +9027,11 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>27/06/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9268,28 +9268,28 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
         <v>5</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F31" s="15" t="n">
@@ -9827,17 +9827,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>511</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8580,17 +8580,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>641</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>405</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>330</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
@@ -8683,11 +8683,11 @@
         <v>10</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8769,11 +8769,11 @@
         <v>23</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8812,11 +8812,11 @@
         <v>7</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8855,11 +8855,11 @@
         <v>5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9113,11 +9113,11 @@
         <v>17</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9268,33 +9268,33 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9483,28 +9483,28 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
         <v>40</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9844,11 +9844,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8515,12 +8515,12 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>05/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -8554,11 +8554,11 @@
         <v>21</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>643</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -8597,16 +8597,16 @@
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -8623,17 +8623,17 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>157</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -8723,14 +8723,14 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8752,17 +8752,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>510</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -8812,16 +8812,16 @@
         <v>7</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9027,11 +9027,11 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9156,11 +9156,11 @@
         <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -9285,11 +9285,11 @@
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9371,11 +9371,11 @@
         <v>55</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -9586,16 +9586,16 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>06/2026</t>
+          <t>07/2026</t>
         </is>
       </c>
     </row>
@@ -9703,28 +9703,28 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>263</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9758,16 +9758,16 @@
         <v>1</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9822,12 +9822,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>332</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9844,16 +9844,16 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8515,12 +8515,12 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>498</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>331</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>27/06/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8687,12 +8687,12 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9311,17 +9311,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>146</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>267</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>261</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8515,7 +8515,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8551,14 +8551,14 @@
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -8580,28 +8580,28 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>408</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>332</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8640,11 +8640,11 @@
         <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -8683,11 +8683,11 @@
         <v>10</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8714,23 +8714,23 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
         <v>274</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8812,11 +8812,11 @@
         <v>7</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8984,7 +8984,7 @@
         <v>6</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9027,11 +9027,11 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9113,11 +9113,11 @@
         <v>17</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9156,11 +9156,11 @@
         <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9199,11 +9199,11 @@
         <v>2</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9273,23 +9273,23 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9328,11 +9328,11 @@
         <v>17</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9371,16 +9371,16 @@
         <v>55</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9497,14 +9497,14 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9586,11 +9586,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9703,23 +9703,23 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9801,7 +9801,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
@@ -9844,11 +9844,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>499</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>153</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -8580,17 +8580,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>646</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>411</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -8628,12 +8628,12 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -8683,11 +8683,11 @@
         <v>10</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8726,11 +8726,11 @@
         <v>274</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8812,11 +8812,11 @@
         <v>7</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8855,16 +8855,16 @@
         <v>5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -8898,11 +8898,11 @@
         <v>20</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F12" s="10" t="n">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9015,12 +9015,12 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F14" s="10" t="n">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9273,28 +9273,28 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9500,16 +9500,16 @@
         <v>41</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
